--- a/astro-site/public/dl/ice-cream-shop-checklist-templates/04-ice-cream-shop-duties-by-role.xlsx
+++ b/astro-site/public/dl/ice-cream-shop-checklist-templates/04-ice-cream-shop-duties-by-role.xlsx
@@ -962,7 +962,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Refill the dipping cabinet with fresh pans (neat visual finish)</t>
+          <t>Refill the dipping cabinet with tempered pans (moved up from the storage freezer ahead of time so they're scoopable; neat visual finish)</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
